--- a/app_kit/tests/TESTS_ROOT/xlsx_for_testing/TaxonProfiles/valid_update/Taxon profiles.xlsx
+++ b/app_kit/tests/TESTS_ROOT/xlsx_for_testing/TaxonProfiles/valid_update/Taxon profiles.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Taxon Profiles" sheetId="1" state="visible" r:id="rId3"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="79">
   <si>
     <t xml:space="preserve">Scientific Name</t>
   </si>
@@ -126,6 +126,9 @@
     <t xml:space="preserve">Quercus robur Forest protection longtext</t>
   </si>
   <si>
+    <t xml:space="preserve">Leaf.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Quercus robur meta_description updated</t>
   </si>
   <si>
@@ -190,9 +193,6 @@
   </si>
   <si>
     <t xml:space="preserve">Primary image (optional)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leaf.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Art Vandeley</t>
@@ -524,37 +524,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -3853,39 +3853,41 @@
       <c r="K4" s="9"/>
       <c r="L4" s="9"/>
       <c r="M4" s="9"/>
-      <c r="N4" s="10"/>
+      <c r="N4" s="10" t="s">
+        <v>34</v>
+      </c>
       <c r="O4" s="10"/>
       <c r="P4" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q4" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R4" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S4" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="T4" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="U4" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="V4" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="W4" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="X4" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="191.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="6" t="s">
@@ -3894,14 +3896,14 @@
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
       <c r="F5" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H5" s="9"/>
       <c r="I5" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J5" s="9"/>
       <c r="K5" s="9"/>
@@ -4170,36 +4172,36 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="17" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="B2" s="17" t="s">
         <v>57</v>
@@ -4264,15 +4266,15 @@
         <v>67</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>8</v>
@@ -4293,7 +4295,7 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>20</v>
@@ -4310,7 +4312,7 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>21</v>
@@ -4325,7 +4327,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>22</v>
@@ -4340,7 +4342,7 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>23</v>
@@ -4355,7 +4357,7 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>24</v>
@@ -4370,7 +4372,7 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>25</v>

--- a/app_kit/tests/TESTS_ROOT/xlsx_for_testing/TaxonProfiles/valid_update/Taxon profiles.xlsx
+++ b/app_kit/tests/TESTS_ROOT/xlsx_for_testing/TaxonProfiles/valid_update/Taxon profiles.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="80">
   <si>
     <t xml:space="preserve">Scientific Name</t>
   </si>
@@ -34,6 +34,9 @@
   </si>
   <si>
     <t xml:space="preserve">Morphotype (optional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Object class (optional)</t>
   </si>
   <si>
     <t xml:space="preserve">short_profile</t>
@@ -627,26 +630,26 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AMP27"/>
+  <dimension ref="A1:AMQ27"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.94"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="38.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="47.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="47.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="38.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="37.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="9" style="2" width="31.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="2" width="23.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="2" width="33.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="2" width="19.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="2" width="62.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="2" width="48.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="2" width="47.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="2" width="46.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="2" width="63.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="2" width="24.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="2" width="24.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="1" width="47.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="47.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="38.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="37.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="10" style="2" width="31.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="2" width="23.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="2" width="33.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="2" width="19.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="2" width="62.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="2" width="48.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="2" width="47.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="2" width="46.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="2" width="63.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="2" width="24.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="2" width="24.21"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -662,33 +665,33 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="4"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="4"/>
+      <c r="J1" s="4" t="s">
+        <v>8</v>
+      </c>
       <c r="K1" s="4"/>
-      <c r="L1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="M1" s="4"/>
-      <c r="N1" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1" s="4"/>
       <c r="O1" s="5" t="s">
         <v>9</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q1" s="5" t="s">
         <v>10</v>
@@ -697,24 +700,26 @@
         <v>11</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T1" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U1" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V1" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W1" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X1" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y1" s="5"/>
+        <v>12</v>
+      </c>
+      <c r="Y1" s="5" t="s">
+        <v>12</v>
+      </c>
       <c r="Z1" s="5"/>
       <c r="AA1" s="5"/>
       <c r="AB1" s="5"/>
@@ -1720,21 +1725,20 @@
       <c r="AMN1" s="5"/>
       <c r="AMO1" s="5"/>
       <c r="AMP1" s="5"/>
+      <c r="AMQ1" s="5"/>
     </row>
     <row r="2" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="4"/>
       <c r="G2" s="4" t="s">
         <v>13</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>14</v>
@@ -1746,24 +1750,24 @@
         <v>16</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="4" t="s">
         <v>18</v>
       </c>
+      <c r="O2" s="5"/>
       <c r="P2" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="Q2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R2" s="5"/>
       <c r="S2" s="5" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T2" s="5" t="s">
         <v>21</v>
@@ -1780,7 +1784,9 @@
       <c r="X2" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="Y2" s="5"/>
+      <c r="Y2" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="Z2" s="5"/>
       <c r="AA2" s="5"/>
       <c r="AB2" s="5"/>
@@ -2786,30 +2792,31 @@
       <c r="AMN2" s="5"/>
       <c r="AMO2" s="5"/>
       <c r="AMP2" s="5"/>
+      <c r="AMQ2" s="5"/>
     </row>
     <row r="3" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="4"/>
+      <c r="E3" s="3"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
-      <c r="J3" s="4" t="s">
-        <v>26</v>
-      </c>
+      <c r="J3" s="4"/>
       <c r="K3" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="N3" s="5"/>
+      <c r="N3" s="4" t="s">
+        <v>28</v>
+      </c>
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
@@ -3826,41 +3833,40 @@
       <c r="AMN3" s="5"/>
       <c r="AMO3" s="5"/>
       <c r="AMP3" s="5"/>
+      <c r="AMQ3" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4" s="6"/>
-      <c r="E4" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="7" t="s">
+      <c r="E4" s="6"/>
+      <c r="F4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="I4" s="9"/>
+      <c r="I4" s="9" t="s">
+        <v>34</v>
+      </c>
       <c r="J4" s="9"/>
       <c r="K4" s="9"/>
       <c r="L4" s="9"/>
       <c r="M4" s="9"/>
-      <c r="N4" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="O4" s="10"/>
-      <c r="P4" s="10" t="s">
+      <c r="N4" s="9"/>
+      <c r="O4" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="Q4" s="11" t="s">
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10" t="s">
         <v>36</v>
       </c>
       <c r="R4" s="11" t="s">
@@ -3872,46 +3878,49 @@
       <c r="T4" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="U4" s="12" t="s">
+      <c r="U4" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="V4" s="11" t="s">
+      <c r="V4" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="W4" s="12" t="s">
+      <c r="W4" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="X4" s="11" t="s">
+      <c r="X4" s="12" t="s">
         <v>43</v>
+      </c>
+      <c r="Y4" s="11" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="191.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
-      <c r="F5" s="9" t="s">
-        <v>45</v>
-      </c>
+      <c r="F5" s="6"/>
       <c r="G5" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9" t="s">
+      <c r="H5" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="J5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9" t="s">
+        <v>48</v>
+      </c>
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
       <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
@@ -3919,9 +3928,9 @@
       <c r="K6" s="7"/>
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
@@ -3929,9 +3938,9 @@
       <c r="K7" s="7"/>
       <c r="L7" s="7"/>
       <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F8" s="7"/>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
@@ -3939,9 +3948,9 @@
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
       <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
       <c r="I9" s="7"/>
@@ -3949,9 +3958,9 @@
       <c r="K9" s="7"/>
       <c r="L9" s="7"/>
       <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F10" s="7"/>
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
       <c r="I10" s="7"/>
@@ -3959,9 +3968,9 @@
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
       <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F11" s="7"/>
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
       <c r="I11" s="7"/>
@@ -3969,9 +3978,9 @@
       <c r="K11" s="7"/>
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F12" s="7"/>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
@@ -3979,9 +3988,9 @@
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
       <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F13" s="7"/>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
       <c r="I13" s="7"/>
@@ -3989,9 +3998,9 @@
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
       <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F14" s="7"/>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
       <c r="I14" s="7"/>
@@ -3999,9 +4008,9 @@
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
       <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F15" s="7"/>
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
@@ -4009,9 +4018,9 @@
       <c r="K15" s="7"/>
       <c r="L15" s="7"/>
       <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F16" s="7"/>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
@@ -4019,9 +4028,9 @@
       <c r="K16" s="7"/>
       <c r="L16" s="7"/>
       <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F17" s="7"/>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
       <c r="I17" s="7"/>
@@ -4029,11 +4038,11 @@
       <c r="K17" s="7"/>
       <c r="L17" s="7"/>
       <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
     </row>
     <row r="18" customFormat="false" ht="112.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
-      <c r="F18" s="13"/>
       <c r="G18" s="13"/>
       <c r="H18" s="13"/>
       <c r="I18" s="13"/>
@@ -4041,9 +4050,9 @@
       <c r="K18" s="13"/>
       <c r="L18" s="13"/>
       <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F19" s="14"/>
       <c r="G19" s="14"/>
       <c r="H19" s="14"/>
       <c r="I19" s="14"/>
@@ -4051,9 +4060,9 @@
       <c r="K19" s="14"/>
       <c r="L19" s="14"/>
       <c r="M19" s="14"/>
+      <c r="N19" s="14"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F20" s="14"/>
       <c r="G20" s="14"/>
       <c r="H20" s="14"/>
       <c r="I20" s="14"/>
@@ -4061,9 +4070,9 @@
       <c r="K20" s="14"/>
       <c r="L20" s="14"/>
       <c r="M20" s="14"/>
+      <c r="N20" s="14"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F21" s="14"/>
       <c r="G21" s="14"/>
       <c r="H21" s="14"/>
       <c r="I21" s="14"/>
@@ -4071,9 +4080,9 @@
       <c r="K21" s="14"/>
       <c r="L21" s="14"/>
       <c r="M21" s="14"/>
+      <c r="N21" s="14"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F22" s="14"/>
       <c r="G22" s="14"/>
       <c r="H22" s="14"/>
       <c r="I22" s="14"/>
@@ -4081,9 +4090,9 @@
       <c r="K22" s="14"/>
       <c r="L22" s="14"/>
       <c r="M22" s="14"/>
+      <c r="N22" s="14"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F23" s="14"/>
       <c r="G23" s="14"/>
       <c r="H23" s="14"/>
       <c r="I23" s="14"/>
@@ -4091,9 +4100,9 @@
       <c r="K23" s="14"/>
       <c r="L23" s="14"/>
       <c r="M23" s="14"/>
+      <c r="N23" s="14"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F24" s="14"/>
       <c r="G24" s="14"/>
       <c r="H24" s="14"/>
       <c r="I24" s="14"/>
@@ -4101,9 +4110,9 @@
       <c r="K24" s="14"/>
       <c r="L24" s="14"/>
       <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F25" s="14"/>
       <c r="G25" s="14"/>
       <c r="H25" s="14"/>
       <c r="I25" s="14"/>
@@ -4111,9 +4120,9 @@
       <c r="K25" s="14"/>
       <c r="L25" s="14"/>
       <c r="M25" s="14"/>
+      <c r="N25" s="14"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F26" s="14"/>
       <c r="G26" s="14"/>
       <c r="H26" s="14"/>
       <c r="I26" s="14"/>
@@ -4121,9 +4130,9 @@
       <c r="K26" s="14"/>
       <c r="L26" s="14"/>
       <c r="M26" s="14"/>
+      <c r="N26" s="14"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F27" s="14"/>
       <c r="G27" s="14"/>
       <c r="H27" s="14"/>
       <c r="I27" s="14"/>
@@ -4131,16 +4140,17 @@
       <c r="K27" s="14"/>
       <c r="L27" s="14"/>
       <c r="M27" s="14"/>
+      <c r="N27" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="H4:M4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:M5"/>
+    <mergeCell ref="I4:N4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:N5"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="U4" r:id="rId1" display="https://samplelib.com/lib/preview/wav/sample-3s.wav"/>
-    <hyperlink ref="W4" r:id="rId2" display="https://code-for-nature.com"/>
+    <hyperlink ref="V4" r:id="rId1" display="https://samplelib.com/lib/preview/wav/sample-3s.wav"/>
+    <hyperlink ref="X4" r:id="rId2" display="https://code-for-nature.com"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
@@ -4172,57 +4182,57 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I2" s="11"/>
     </row>
@@ -4251,60 +4261,60 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D1" s="16" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
@@ -4312,13 +4322,13 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
@@ -4327,13 +4337,13 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
@@ -4342,13 +4352,13 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
@@ -4357,13 +4367,13 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
@@ -4372,13 +4382,13 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -4390,8 +4400,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>